--- a/business_surveys/040_food_insecurity_in_urban_areas_survey--business_surveys.xlsx
+++ b/business_surveys/040_food_insecurity_in_urban_areas_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -845,12 +845,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'no_challenge'}</t>
+          <t>no_challenge</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'No challenge'}</t>
+          <t>No challenge</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'food_insecurity'}</t>
+          <t>food_insecurity</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Food insecurity'}</t>
+          <t>Food insecurity</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'lack_of_money'}</t>
+          <t>lack_of_money</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Lack of money'}</t>
+          <t>Lack of money</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'limited_access'}</t>
+          <t>limited_access</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Limited access'}</t>
+          <t>Limited access</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'no_coping'}</t>
+          <t>no_coping</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'No coping'}</t>
+          <t>No coping</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'food_bank'}</t>
+          <t>food_bank</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Food bank'}</t>
+          <t>Food bank</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'government_help'}</t>
+          <t>government_help</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Government help'}</t>
+          <t>Government help</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'other_help'}</t>
+          <t>other_help</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Other help'}</t>
+          <t>Other help</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'self_help'}</t>
+          <t>self_help</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Self help'}</t>
+          <t>Self help</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'store'}</t>
+          <t>store</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Store'}</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'supermarket'}</t>
+          <t>supermarket</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Supermarket'}</t>
+          <t>Supermarket</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'farm'}</t>
+          <t>farm</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Farm'}</t>
+          <t>Farm</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'urban'}</t>
+          <t>urban</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Urban'}</t>
+          <t>Urban</t>
         </is>
       </c>
     </row>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'rural'}</t>
+          <t>rural</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Rural'}</t>
+          <t>Rural</t>
         </is>
       </c>
     </row>
@@ -1218,12 +1218,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'employment'}</t>
+          <t>employment</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Employment'}</t>
+          <t>Employment</t>
         </is>
       </c>
     </row>
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'government_aid'}</t>
+          <t>government_aid</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Government aid'}</t>
+          <t>Government aid</t>
         </is>
       </c>
     </row>
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1286,46 +1286,46 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'self_employed'}</t>
+          <t>self_employed</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Self employed'}</t>
+          <t>Self employed</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>household_income_source_choices</t>
+          <t>household_income_frequency_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>household_income_source_choices</t>
+          <t>household_income_frequency_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'monthly'}</t>
+          <t>bi_weekly</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Monthly'}</t>
+          <t>Bi weekly</t>
         </is>
       </c>
     </row>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'weekly'}</t>
+          <t>fortnightly</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Weekly'}</t>
+          <t>Fortnightly</t>
         </is>
       </c>
     </row>
@@ -1371,131 +1371,63 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'bi_weekly'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Bi weekly'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>household_income_frequency_choices</t>
+          <t>household_income_type_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'fortnightly'}</t>
+          <t>fixed_income</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Fortnightly'}</t>
+          <t>Fixed income</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>household_income_frequency_choices</t>
+          <t>household_income_type_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>variable_income</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Variable income</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>household_income_frequency_choices</t>
+          <t>household_income_type_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>household_income_type_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>{'label':_'fixed_income'}</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>{'label': 'Fixed income'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>household_income_type_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>{'label':_'variable_income'}</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>{'label': 'Variable income'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>household_income_type_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>{'label':_'other'}</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>{'label': 'Other'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>household_income_type_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>{'label':_'other'}</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
